--- a/exports/report-detail.xlsx
+++ b/exports/report-detail.xlsx
@@ -12,48 +12,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>FULL NAME</t>
   </si>
   <si>
-    <t>CHARGEABLE INCOME</t>
-  </si>
-  <si>
-    <t>Transport Allowance</t>
-  </si>
-  <si>
-    <t>Pension Fund</t>
-  </si>
-  <si>
-    <t>ANNUAL EMPLOYEE PENSION @ 8%</t>
+    <t>Gross Pay</t>
   </si>
   <si>
     <t>National Housing Fund</t>
   </si>
   <si>
-    <t>ANNUAL CONSOLIDATED ALLOWANCE</t>
-  </si>
-  <si>
-    <t>Total Deduction</t>
-  </si>
-  <si>
-    <t>Housing Allowance</t>
-  </si>
-  <si>
-    <t>StartDate</t>
-  </si>
-  <si>
-    <t>Employer Pension Contribution</t>
-  </si>
-  <si>
     <t>Net Pay</t>
   </si>
   <si>
-    <t>Darron Veum</t>
+    <t>admin User</t>
   </si>
   <si>
-    <t>2025-09-01</t>
+    <t>Berniece Haag</t>
   </si>
 </sst>
 </file>
@@ -122,21 +98,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.0" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="18.81640625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.87890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="15.0" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.60546875" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="15.0" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="29.17578125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="19.60546875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="32.05078125" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="15.0" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="16.5625" customWidth="true" bestFit="true"/>
-    <col min="10" max="10" width="15.0" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="26.36328125" customWidth="true" bestFit="true"/>
-    <col min="12" max="12" width="15.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -152,67 +120,33 @@
       <c r="D1" t="s" s="1">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="1">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s" s="1">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s" s="1">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s" s="1">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s" s="1">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s" s="1">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s" s="1">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s" s="1">
-        <v>11</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B2" t="n" s="3">
-        <v>7863366.34</v>
+        <v>1050868.05</v>
       </c>
       <c r="C2" t="n" s="3">
-        <v>60853.99</v>
+        <v>0.0</v>
       </c>
       <c r="D2" t="n" s="3">
-        <v>19473.28</v>
+        <v>864475.0</v>
       </c>
-      <c r="E2" t="n" s="3">
-        <v>272625.9</v>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>5</v>
       </c>
-      <c r="F2" t="n" s="3">
+      <c r="B3" t="n" s="3">
+        <v>1050868.05</v>
+      </c>
+      <c r="C3" t="n" s="3">
         <v>0.0</v>
       </c>
-      <c r="G2" t="n" s="3">
-        <v>2215841.58</v>
-      </c>
-      <c r="H2" t="n" s="3">
-        <v>159645.99</v>
-      </c>
-      <c r="I2" t="n" s="3">
-        <v>60853.99</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>13</v>
-      </c>
-      <c r="K2" t="n" s="3">
-        <v>24341.58</v>
-      </c>
-      <c r="L2" t="n" s="3">
-        <v>749501.0</v>
+      <c r="D3" t="n" s="3">
+        <v>864475.0</v>
       </c>
     </row>
   </sheetData>
